--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101760782</v>
+        <v>101972023</v>
       </c>
       <c r="B2" t="n">
-        <v>5207</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100155</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre timmerman</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acanthocinus griseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -736,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578782.9229361662</v>
+        <v>578783</v>
       </c>
       <c r="R2" t="n">
-        <v>6337435.662723515</v>
+        <v>6337436</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -766,27 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
+          <t>2022-06-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På färska timmerhögar med gran och tall</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,78 +797,69 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Oscar Nordahl</t>
+          <t>Oscar Nordahl, Joakim Holm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101960910</v>
+        <v>102353836</v>
       </c>
       <c r="B3" t="n">
-        <v>5188</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>40267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101424</v>
+        <v>101166</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulröd blankbock</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Obrium cantharinum</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>puppa</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>S Hultet, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578782.9229361662</v>
+        <v>578783</v>
       </c>
       <c r="R3" t="n">
-        <v>6337435.662723515</v>
+        <v>6337436</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -910,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -925,7 +906,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flög runt, och kröp på, färska timmerhögar med framförallt grov gran men med visst inslag av asp</t>
+          <t>På grov asp-stam i timmerhög. Den yttersta delen av puppan stack ut ur kläckhålet (uttagen på bilden). Fyra ex av grön aspvedbock sprang runt på samma stam.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -953,15 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101972023</v>
+        <v>101960910</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,26 +945,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>101424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gulröd blankbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Obrium cantharinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1014,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578782.9229361662</v>
+        <v>578783</v>
       </c>
       <c r="R4" t="n">
-        <v>6337435.662723515</v>
+        <v>6337436</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1049,7 +1025,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1060,6 +1036,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>03:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög runt, och kröp på, färska timmerhögar med framförallt grov gran men med visst inslag av asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1087,71 +1068,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101960968</v>
+        <v>101984142</v>
       </c>
       <c r="B5" t="n">
-        <v>5295</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101728</v>
+        <v>102118</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>S Hultet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578782.9229361662</v>
+        <v>578783</v>
       </c>
       <c r="R5" t="n">
-        <v>6337435.662723515</v>
+        <v>6337436</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1183,7 +1150,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1196,18 +1163,12 @@
           <t>03:00</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4 ex på aspstammar i timmerhög. Resterande 7 ex på en kvarlämnad, levande, grov asp ute på hygget strax intill högarna. Parning observerades.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1229,16 +1190,11 @@
         <v>101972020</v>
       </c>
       <c r="B6" t="n">
-        <v>8721</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1287,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578782.9229361662</v>
+        <v>578783</v>
       </c>
       <c r="R6" t="n">
-        <v>6337435.662723515</v>
+        <v>6337436</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1357,141 +1313,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>102353836</v>
-      </c>
-      <c r="B7" t="n">
-        <v>39582</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>101166</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mindre träfjäril</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Acossus terebra</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>puppa</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>S Hultet, Sm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>578782.9229361662</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6337435.662723515</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På grov asp-stam i timmerhög. Den yttersta delen av puppan stack ut ur kläckhålet (uttagen på bilden). Fyra ex av grön aspvedbock sprang runt på samma stam.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Oscar Nordahl</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Oscar Nordahl, Joakim Holm</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10103-2022 artfynd.xlsx
+++ b/artfynd/A 10103-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101972023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -931,6 +941,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102353836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,6 +1080,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101960910</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1184,6 +1204,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101984142</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1313,8 +1338,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101972020</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>